--- a/Experiment/Orders/PAR01_RUN01.xlsx
+++ b/Experiment/Orders/PAR01_RUN01.xlsx
@@ -174,166 +174,166 @@
     <t>Hand_01_R.png</t>
   </si>
   <si>
+    <t>Face_16_L.png</t>
+  </si>
+  <si>
+    <t>Face_07_R.png</t>
+  </si>
+  <si>
+    <t>Object_04_R.png</t>
+  </si>
+  <si>
+    <t>Object_07_L.png</t>
+  </si>
+  <si>
+    <t>Hand_08_R.png</t>
+  </si>
+  <si>
+    <t>Hand_03_R.png</t>
+  </si>
+  <si>
+    <t>Face_08_R.png</t>
+  </si>
+  <si>
+    <t>Face_02_R.png</t>
+  </si>
+  <si>
+    <t>Hand_12_L.png</t>
+  </si>
+  <si>
+    <t>Face_12_R.png</t>
+  </si>
+  <si>
+    <t>Hand_16_R.png</t>
+  </si>
+  <si>
+    <t>Hand_08_L.png</t>
+  </si>
+  <si>
+    <t>Object_01_R.png</t>
+  </si>
+  <si>
+    <t>Object_11_R.png</t>
+  </si>
+  <si>
+    <t>Face_10_R.png</t>
+  </si>
+  <si>
+    <t>Object_03_L.png</t>
+  </si>
+  <si>
+    <t>Face_14_L.png</t>
+  </si>
+  <si>
+    <t>Hand_10_R.png</t>
+  </si>
+  <si>
+    <t>Object_16_R.png</t>
+  </si>
+  <si>
+    <t>Face_09_L.png</t>
+  </si>
+  <si>
+    <t>Face_11_L.png</t>
+  </si>
+  <si>
+    <t>Object_02_R.png</t>
+  </si>
+  <si>
+    <t>Hand_09_R.png</t>
+  </si>
+  <si>
+    <t>Object_11_L.png</t>
+  </si>
+  <si>
+    <t>Object_10_R.png</t>
+  </si>
+  <si>
+    <t>Object_12_L.png</t>
+  </si>
+  <si>
+    <t>Object_01_L.png</t>
+  </si>
+  <si>
+    <t>Face_16_R.png</t>
+  </si>
+  <si>
+    <t>Face_02_L.png</t>
+  </si>
+  <si>
+    <t>Hand_06_L.png</t>
+  </si>
+  <si>
+    <t>Face_15_L.png</t>
+  </si>
+  <si>
+    <t>Object_06_L.png</t>
+  </si>
+  <si>
     <t>Hand_11_L.png</t>
   </si>
   <si>
+    <t>Hand_12_R.png</t>
+  </si>
+  <si>
+    <t>Hand_10_L.png</t>
+  </si>
+  <si>
+    <t>Face_13_L.png</t>
+  </si>
+  <si>
+    <t>Object_10_L.png</t>
+  </si>
+  <si>
+    <t>Object_06_R.png</t>
+  </si>
+  <si>
+    <t>Face_08_L.png</t>
+  </si>
+  <si>
+    <t>Face_11_R.png</t>
+  </si>
+  <si>
+    <t>Hand_13_R.png</t>
+  </si>
+  <si>
+    <t>Object_13_L.png</t>
+  </si>
+  <si>
+    <t>Face_06_R.png</t>
+  </si>
+  <si>
+    <t>Object_04_L.png</t>
+  </si>
+  <si>
+    <t>Face_03_L.png</t>
+  </si>
+  <si>
+    <t>Hand_06_R.png</t>
+  </si>
+  <si>
+    <t>Face_05_L.png</t>
+  </si>
+  <si>
+    <t>Object_15_R.png</t>
+  </si>
+  <si>
+    <t>Hand_07_R.png</t>
+  </si>
+  <si>
+    <t>Face_04_R.png</t>
+  </si>
+  <si>
+    <t>Hand_02_L.png</t>
+  </si>
+  <si>
+    <t>Object_05_R.png</t>
+  </si>
+  <si>
+    <t>Hand_15_L.png</t>
+  </si>
+  <si>
     <t>Face_05_R.png</t>
-  </si>
-  <si>
-    <t>Object_10_R.png</t>
-  </si>
-  <si>
-    <t>Object_07_L.png</t>
-  </si>
-  <si>
-    <t>Hand_08_R.png</t>
-  </si>
-  <si>
-    <t>Hand_09_R.png</t>
-  </si>
-  <si>
-    <t>Face_08_R.png</t>
-  </si>
-  <si>
-    <t>Face_02_R.png</t>
-  </si>
-  <si>
-    <t>Hand_12_L.png</t>
-  </si>
-  <si>
-    <t>Object_05_R.png</t>
-  </si>
-  <si>
-    <t>Hand_06_R.png</t>
-  </si>
-  <si>
-    <t>Face_11_L.png</t>
-  </si>
-  <si>
-    <t>Face_07_R.png</t>
-  </si>
-  <si>
-    <t>Face_15_L.png</t>
-  </si>
-  <si>
-    <t>Hand_13_R.png</t>
-  </si>
-  <si>
-    <t>Object_03_L.png</t>
-  </si>
-  <si>
-    <t>Face_14_L.png</t>
-  </si>
-  <si>
-    <t>Object_04_R.png</t>
-  </si>
-  <si>
-    <t>Object_02_R.png</t>
-  </si>
-  <si>
-    <t>Face_08_L.png</t>
-  </si>
-  <si>
-    <t>Hand_06_L.png</t>
-  </si>
-  <si>
-    <t>Face_02_L.png</t>
-  </si>
-  <si>
-    <t>Object_04_L.png</t>
-  </si>
-  <si>
-    <t>Object_01_L.png</t>
-  </si>
-  <si>
-    <t>Face_16_R.png</t>
-  </si>
-  <si>
-    <t>Object_13_L.png</t>
-  </si>
-  <si>
-    <t>Object_11_R.png</t>
-  </si>
-  <si>
-    <t>Face_12_R.png</t>
-  </si>
-  <si>
-    <t>Hand_03_R.png</t>
-  </si>
-  <si>
-    <t>Object_01_R.png</t>
-  </si>
-  <si>
-    <t>Face_03_L.png</t>
-  </si>
-  <si>
-    <t>Face_05_L.png</t>
-  </si>
-  <si>
-    <t>Hand_12_R.png</t>
-  </si>
-  <si>
-    <t>Hand_15_L.png</t>
-  </si>
-  <si>
-    <t>Face_16_L.png</t>
-  </si>
-  <si>
-    <t>Object_11_L.png</t>
-  </si>
-  <si>
-    <t>Object_16_R.png</t>
-  </si>
-  <si>
-    <t>Hand_10_L.png</t>
-  </si>
-  <si>
-    <t>Hand_07_R.png</t>
-  </si>
-  <si>
-    <t>Face_10_R.png</t>
-  </si>
-  <si>
-    <t>Object_10_L.png</t>
-  </si>
-  <si>
-    <t>Hand_10_R.png</t>
-  </si>
-  <si>
-    <t>Object_12_L.png</t>
-  </si>
-  <si>
-    <t>Face_13_L.png</t>
-  </si>
-  <si>
-    <t>Object_15_R.png</t>
-  </si>
-  <si>
-    <t>Face_04_R.png</t>
-  </si>
-  <si>
-    <t>Hand_08_L.png</t>
-  </si>
-  <si>
-    <t>Face_11_R.png</t>
-  </si>
-  <si>
-    <t>Object_06_R.png</t>
-  </si>
-  <si>
-    <t>Object_06_L.png</t>
-  </si>
-  <si>
-    <t>Face_06_R.png</t>
-  </si>
-  <si>
-    <t>Hand_16_R.png</t>
-  </si>
-  <si>
-    <t>Face_09_L.png</t>
-  </si>
-  <si>
-    <t>Hand_02_L.png</t>
   </si>
   <si>
     <t>Filename_right</t>
@@ -602,7 +602,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D4" s="0"/>
       <c r="E4" s="0"/>
@@ -666,7 +666,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D6" s="0"/>
       <c r="E6" s="0"/>
@@ -986,7 +986,7 @@
         <v>2</v>
       </c>
       <c r="C16" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D16" s="0"/>
       <c r="E16" s="0"/>
@@ -1020,7 +1020,7 @@
         <v>18</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="F17" s="0" t="s">
         <v>109</v>
@@ -1050,7 +1050,7 @@
         <v>2</v>
       </c>
       <c r="C18" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D18" s="0"/>
       <c r="E18" s="0"/>
@@ -1084,7 +1084,7 @@
         <v>19</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="F19" s="0" t="s">
         <v>109</v>
@@ -1114,7 +1114,7 @@
         <v>2</v>
       </c>
       <c r="C20" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D20" s="0"/>
       <c r="E20" s="0"/>
@@ -1178,7 +1178,7 @@
         <v>2</v>
       </c>
       <c r="C22" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D22" s="0"/>
       <c r="E22" s="0"/>
@@ -1212,7 +1212,7 @@
         <v>21</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F23" s="0" t="s">
         <v>109</v>
@@ -1468,7 +1468,7 @@
         <v>25</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="F31" s="0" t="s">
         <v>109</v>
@@ -1498,7 +1498,7 @@
         <v>2</v>
       </c>
       <c r="C32" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D32" s="0"/>
       <c r="E32" s="0"/>
@@ -1596,7 +1596,7 @@
         <v>27</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="F35" s="0" t="s">
         <v>109</v>
@@ -1690,7 +1690,7 @@
         <v>2</v>
       </c>
       <c r="C38" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D38" s="0"/>
       <c r="E38" s="0"/>
@@ -1715,35 +1715,35 @@
         <v>19</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C39" s="0">
         <v>1</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="F39" s="0" t="s">
         <v>109</v>
       </c>
       <c r="G39" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" s="0"/>
       <c r="I39" s="0" t="s">
         <v>113</v>
       </c>
       <c r="J39" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K39" s="0" t="s">
         <v>119</v>
       </c>
       <c r="L39" s="0" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="40">
@@ -1779,16 +1779,16 @@
         <v>20</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C41" s="0">
         <v>1</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E41" s="0" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="F41" s="0" t="s">
         <v>109</v>
@@ -1804,10 +1804,10 @@
         <v>116</v>
       </c>
       <c r="K41" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L41" s="0" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="42">
@@ -1818,7 +1818,7 @@
         <v>2</v>
       </c>
       <c r="C42" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D42" s="0"/>
       <c r="E42" s="0"/>
@@ -1849,10 +1849,10 @@
         <v>1</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="F43" s="0" t="s">
         <v>109</v>
@@ -1871,7 +1871,7 @@
         <v>118</v>
       </c>
       <c r="L43" s="0" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
     </row>
     <row r="44">
@@ -1907,16 +1907,16 @@
         <v>22</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C45" s="0">
         <v>1</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="F45" s="0" t="s">
         <v>109</v>
@@ -1932,10 +1932,10 @@
         <v>116</v>
       </c>
       <c r="K45" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L45" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="46">
@@ -1946,7 +1946,7 @@
         <v>2</v>
       </c>
       <c r="C46" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D46" s="0"/>
       <c r="E46" s="0"/>
@@ -1971,16 +1971,16 @@
         <v>23</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C47" s="0">
         <v>1</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E47" s="0" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="F47" s="0" t="s">
         <v>109</v>
@@ -1996,10 +1996,10 @@
         <v>116</v>
       </c>
       <c r="K47" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L47" s="0" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
     </row>
     <row r="48">
@@ -2035,16 +2035,16 @@
         <v>24</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C49" s="0">
         <v>1</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E49" s="0" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F49" s="0" t="s">
         <v>109</v>
@@ -2060,10 +2060,10 @@
         <v>116</v>
       </c>
       <c r="K49" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L49" s="0" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
     </row>
     <row r="50">
@@ -2099,16 +2099,16 @@
         <v>25</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C51" s="0">
         <v>1</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E51" s="0" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="F51" s="0" t="s">
         <v>109</v>
@@ -2124,10 +2124,10 @@
         <v>116</v>
       </c>
       <c r="K51" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L51" s="0" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="52">
@@ -2138,7 +2138,7 @@
         <v>2</v>
       </c>
       <c r="C52" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D52" s="0"/>
       <c r="E52" s="0"/>
@@ -2163,16 +2163,16 @@
         <v>26</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C53" s="0">
         <v>1</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E53" s="0" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="F53" s="0" t="s">
         <v>109</v>
@@ -2185,13 +2185,13 @@
         <v>113</v>
       </c>
       <c r="J53" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K53" s="0" t="s">
         <v>120</v>
       </c>
       <c r="L53" s="0" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="54">
@@ -2202,7 +2202,7 @@
         <v>2</v>
       </c>
       <c r="C54" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D54" s="0"/>
       <c r="E54" s="0"/>
@@ -2233,10 +2233,10 @@
         <v>1</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E55" s="0" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F55" s="0" t="s">
         <v>109</v>
@@ -2255,7 +2255,7 @@
         <v>120</v>
       </c>
       <c r="L55" s="0" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="56">
@@ -2266,7 +2266,7 @@
         <v>2</v>
       </c>
       <c r="C56" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D56" s="0"/>
       <c r="E56" s="0"/>
@@ -2291,16 +2291,16 @@
         <v>28</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C57" s="0">
         <v>1</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E57" s="0" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F57" s="0" t="s">
         <v>109</v>
@@ -2316,10 +2316,10 @@
         <v>115</v>
       </c>
       <c r="K57" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L57" s="0" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58">
@@ -2330,7 +2330,7 @@
         <v>2</v>
       </c>
       <c r="C58" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D58" s="0"/>
       <c r="E58" s="0"/>
@@ -2355,16 +2355,16 @@
         <v>29</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C59" s="0">
         <v>1</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F59" s="0" t="s">
         <v>109</v>
@@ -2380,10 +2380,10 @@
         <v>115</v>
       </c>
       <c r="K59" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L59" s="0" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="60">
@@ -2419,16 +2419,16 @@
         <v>30</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C61" s="0">
         <v>1</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>98</v>
+        <v>39</v>
       </c>
       <c r="F61" s="0" t="s">
         <v>109</v>
@@ -2441,13 +2441,13 @@
         <v>113</v>
       </c>
       <c r="J61" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K61" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L61" s="0" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
     </row>
     <row r="62">
@@ -2483,16 +2483,16 @@
         <v>31</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C63" s="0">
         <v>1</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E63" s="0" t="s">
-        <v>41</v>
+        <v>102</v>
       </c>
       <c r="F63" s="0" t="s">
         <v>109</v>
@@ -2505,13 +2505,13 @@
         <v>113</v>
       </c>
       <c r="J63" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K63" s="0" t="s">
         <v>119</v>
       </c>
       <c r="L63" s="0" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
     </row>
     <row r="64">
@@ -2547,16 +2547,16 @@
         <v>32</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C65" s="0">
         <v>1</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="F65" s="0" t="s">
         <v>109</v>
@@ -2569,13 +2569,13 @@
         <v>113</v>
       </c>
       <c r="J65" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K65" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L65" s="0" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
     </row>
     <row r="66">
@@ -2611,16 +2611,16 @@
         <v>33</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C67" s="0">
         <v>1</v>
       </c>
       <c r="D67" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E67" s="0" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="F67" s="0" t="s">
         <v>109</v>
@@ -2633,13 +2633,13 @@
         <v>113</v>
       </c>
       <c r="J67" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K67" s="0" t="s">
         <v>118</v>
       </c>
       <c r="L67" s="0" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="68">
@@ -2675,16 +2675,16 @@
         <v>34</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C69" s="0">
         <v>1</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="F69" s="0" t="s">
         <v>109</v>
@@ -2697,13 +2697,13 @@
         <v>113</v>
       </c>
       <c r="J69" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K69" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L69" s="0" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="70">
@@ -2739,16 +2739,16 @@
         <v>35</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C71" s="0">
         <v>1</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="F71" s="0" t="s">
         <v>109</v>
@@ -2764,10 +2764,10 @@
         <v>116</v>
       </c>
       <c r="K71" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L71" s="0" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="72">
@@ -2803,16 +2803,16 @@
         <v>36</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C73" s="0">
         <v>1</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E73" s="0" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="F73" s="0" t="s">
         <v>109</v>
@@ -2825,13 +2825,13 @@
         <v>113</v>
       </c>
       <c r="J73" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K73" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L73" s="0" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
     </row>
     <row r="74">
@@ -2867,16 +2867,16 @@
         <v>37</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C75" s="0">
         <v>1</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E75" s="0" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="F75" s="0" t="s">
         <v>109</v>
@@ -2889,13 +2889,13 @@
         <v>113</v>
       </c>
       <c r="J75" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K75" s="0" t="s">
         <v>120</v>
       </c>
       <c r="L75" s="0" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
     </row>
     <row r="76">
@@ -2906,7 +2906,7 @@
         <v>2</v>
       </c>
       <c r="C76" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D76" s="0"/>
       <c r="E76" s="0"/>
@@ -2937,10 +2937,10 @@
         <v>1</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="F77" s="0" t="s">
         <v>109</v>
@@ -2959,7 +2959,7 @@
         <v>120</v>
       </c>
       <c r="L77" s="0" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="78">
@@ -2970,7 +2970,7 @@
         <v>2</v>
       </c>
       <c r="C78" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D78" s="0"/>
       <c r="E78" s="0"/>
@@ -3001,10 +3001,10 @@
         <v>1</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E79" s="0" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F79" s="0" t="s">
         <v>109</v>
@@ -3023,7 +3023,7 @@
         <v>120</v>
       </c>
       <c r="L79" s="0" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="80">
@@ -3034,7 +3034,7 @@
         <v>2</v>
       </c>
       <c r="C80" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D80" s="0"/>
       <c r="E80" s="0"/>
@@ -3059,16 +3059,16 @@
         <v>40</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C81" s="0">
         <v>1</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="F81" s="0" t="s">
         <v>109</v>
@@ -3084,10 +3084,10 @@
         <v>116</v>
       </c>
       <c r="K81" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L81" s="0" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="82">
@@ -3123,16 +3123,16 @@
         <v>41</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C83" s="0">
         <v>1</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="F83" s="0" t="s">
         <v>109</v>
@@ -3148,10 +3148,10 @@
         <v>116</v>
       </c>
       <c r="K83" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L83" s="0" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
     </row>
     <row r="84">
@@ -3162,7 +3162,7 @@
         <v>2</v>
       </c>
       <c r="C84" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D84" s="0"/>
       <c r="E84" s="0"/>
@@ -3187,16 +3187,16 @@
         <v>42</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C85" s="0">
         <v>1</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E85" s="0" t="s">
-        <v>52</v>
+        <v>101</v>
       </c>
       <c r="F85" s="0" t="s">
         <v>109</v>
@@ -3209,13 +3209,13 @@
         <v>113</v>
       </c>
       <c r="J85" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K85" s="0" t="s">
         <v>120</v>
       </c>
       <c r="L85" s="0" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
     </row>
     <row r="86">
@@ -3251,16 +3251,16 @@
         <v>43</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C87" s="0">
         <v>1</v>
       </c>
       <c r="D87" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E87" s="0" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F87" s="0" t="s">
         <v>109</v>
@@ -3273,13 +3273,13 @@
         <v>113</v>
       </c>
       <c r="J87" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K87" s="0" t="s">
         <v>120</v>
       </c>
       <c r="L87" s="0" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
     </row>
     <row r="88">
@@ -3315,7 +3315,7 @@
         <v>44</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C89" s="0">
         <v>1</v>
@@ -3324,13 +3324,13 @@
         <v>53</v>
       </c>
       <c r="E89" s="0" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="F89" s="0" t="s">
         <v>109</v>
       </c>
       <c r="G89" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H89" s="0"/>
       <c r="I89" s="0" t="s">
@@ -3340,10 +3340,10 @@
         <v>116</v>
       </c>
       <c r="K89" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L89" s="0" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="90">
@@ -3354,7 +3354,7 @@
         <v>2</v>
       </c>
       <c r="C90" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D90" s="0"/>
       <c r="E90" s="0"/>
@@ -3407,7 +3407,7 @@
         <v>119</v>
       </c>
       <c r="L91" s="0" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="92">
@@ -3471,7 +3471,7 @@
         <v>118</v>
       </c>
       <c r="L93" s="0" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
     </row>
     <row r="94">
@@ -3482,7 +3482,7 @@
         <v>2</v>
       </c>
       <c r="C94" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D94" s="0"/>
       <c r="E94" s="0"/>
@@ -3610,7 +3610,7 @@
         <v>2</v>
       </c>
       <c r="C98" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D98" s="0"/>
       <c r="E98" s="0"/>
@@ -3663,7 +3663,7 @@
         <v>120</v>
       </c>
       <c r="L99" s="0" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="100">
@@ -3674,7 +3674,7 @@
         <v>2</v>
       </c>
       <c r="C100" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D100" s="0"/>
       <c r="E100" s="0"/>
@@ -3738,7 +3738,7 @@
         <v>2</v>
       </c>
       <c r="C102" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D102" s="0"/>
       <c r="E102" s="0"/>
@@ -3836,7 +3836,7 @@
         <v>61</v>
       </c>
       <c r="E105" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F105" s="0" t="s">
         <v>109</v>
@@ -3891,7 +3891,7 @@
         <v>53</v>
       </c>
       <c r="B107" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C107" s="0">
         <v>1</v>
@@ -3916,10 +3916,10 @@
         <v>115</v>
       </c>
       <c r="K107" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L107" s="0" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="108">
@@ -3983,7 +3983,7 @@
         <v>120</v>
       </c>
       <c r="L109" s="0" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="110">
@@ -4019,7 +4019,7 @@
         <v>55</v>
       </c>
       <c r="B111" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C111" s="0">
         <v>1</v>
@@ -4028,7 +4028,7 @@
         <v>64</v>
       </c>
       <c r="E111" s="0" t="s">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="F111" s="0" t="s">
         <v>109</v>
@@ -4044,10 +4044,10 @@
         <v>116</v>
       </c>
       <c r="K111" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L111" s="0" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="112">
@@ -4083,7 +4083,7 @@
         <v>56</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C113" s="0">
         <v>1</v>
@@ -4108,10 +4108,10 @@
         <v>115</v>
       </c>
       <c r="K113" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L113" s="0" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="114">
@@ -4122,7 +4122,7 @@
         <v>2</v>
       </c>
       <c r="C114" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D114" s="0"/>
       <c r="E114" s="0"/>
@@ -4147,7 +4147,7 @@
         <v>57</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C115" s="0">
         <v>1</v>
@@ -4156,7 +4156,7 @@
         <v>66</v>
       </c>
       <c r="E115" s="0" t="s">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="F115" s="0" t="s">
         <v>109</v>
@@ -4169,13 +4169,13 @@
         <v>113</v>
       </c>
       <c r="J115" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K115" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L115" s="0" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
     </row>
     <row r="116">
@@ -4211,7 +4211,7 @@
         <v>58</v>
       </c>
       <c r="B117" s="0" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C117" s="0">
         <v>1</v>
@@ -4236,10 +4236,10 @@
         <v>115</v>
       </c>
       <c r="K117" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L117" s="0" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="118">
@@ -4250,7 +4250,7 @@
         <v>2</v>
       </c>
       <c r="C118" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D118" s="0"/>
       <c r="E118" s="0"/>
@@ -4403,7 +4403,7 @@
         <v>61</v>
       </c>
       <c r="B123" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C123" s="0">
         <v>1</v>
@@ -4428,10 +4428,10 @@
         <v>115</v>
       </c>
       <c r="K123" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L123" s="0" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="124">
@@ -4442,7 +4442,7 @@
         <v>2</v>
       </c>
       <c r="C124" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D124" s="0"/>
       <c r="E124" s="0"/>
@@ -4495,7 +4495,7 @@
         <v>118</v>
       </c>
       <c r="L125" s="0" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="126">
@@ -4540,7 +4540,7 @@
         <v>72</v>
       </c>
       <c r="E127" s="0" t="s">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="F127" s="0" t="s">
         <v>109</v>
@@ -4559,7 +4559,7 @@
         <v>119</v>
       </c>
       <c r="L127" s="0" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="128">
@@ -4570,7 +4570,7 @@
         <v>2</v>
       </c>
       <c r="C128" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D128" s="0"/>
       <c r="E128" s="0"/>
@@ -4595,7 +4595,7 @@
         <v>64</v>
       </c>
       <c r="B129" s="0" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C129" s="0">
         <v>1</v>
@@ -4604,7 +4604,7 @@
         <v>73</v>
       </c>
       <c r="E129" s="0" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="F129" s="0" t="s">
         <v>109</v>
@@ -4620,10 +4620,10 @@
         <v>116</v>
       </c>
       <c r="K129" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L129" s="0" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="130">
@@ -4634,7 +4634,7 @@
         <v>2</v>
       </c>
       <c r="C130" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D130" s="0"/>
       <c r="E130" s="0"/>
@@ -4659,7 +4659,7 @@
         <v>65</v>
       </c>
       <c r="B131" s="0" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C131" s="0">
         <v>1</v>
@@ -4668,7 +4668,7 @@
         <v>74</v>
       </c>
       <c r="E131" s="0" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="F131" s="0" t="s">
         <v>109</v>
@@ -4681,10 +4681,10 @@
         <v>113</v>
       </c>
       <c r="J131" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K131" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L131" s="0" t="s">
         <v>132</v>
@@ -4723,7 +4723,7 @@
         <v>66</v>
       </c>
       <c r="B133" s="0" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C133" s="0">
         <v>1</v>
@@ -4732,7 +4732,7 @@
         <v>75</v>
       </c>
       <c r="E133" s="0" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F133" s="0" t="s">
         <v>109</v>
@@ -4745,13 +4745,13 @@
         <v>113</v>
       </c>
       <c r="J133" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K133" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L133" s="0" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
     </row>
     <row r="134">
@@ -4796,7 +4796,7 @@
         <v>76</v>
       </c>
       <c r="E135" s="0" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="F135" s="0" t="s">
         <v>109</v>
@@ -4815,7 +4815,7 @@
         <v>118</v>
       </c>
       <c r="L135" s="0" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
     </row>
     <row r="136">
@@ -4826,7 +4826,7 @@
         <v>2</v>
       </c>
       <c r="C136" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D136" s="0"/>
       <c r="E136" s="0"/>
@@ -4851,35 +4851,35 @@
         <v>68</v>
       </c>
       <c r="B137" s="0" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C137" s="0">
         <v>1</v>
       </c>
       <c r="D137" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E137" s="0" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F137" s="0" t="s">
         <v>109</v>
       </c>
       <c r="G137" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H137" s="0"/>
       <c r="I137" s="0" t="s">
         <v>113</v>
       </c>
       <c r="J137" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K137" s="0" t="s">
         <v>118</v>
       </c>
       <c r="L137" s="0" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="138">
@@ -4915,16 +4915,16 @@
         <v>69</v>
       </c>
       <c r="B139" s="0" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C139" s="0">
         <v>1</v>
       </c>
       <c r="D139" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E139" s="0" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
       <c r="F139" s="0" t="s">
         <v>109</v>
@@ -4937,13 +4937,13 @@
         <v>113</v>
       </c>
       <c r="J139" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K139" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L139" s="0" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="140">
@@ -4954,7 +4954,7 @@
         <v>2</v>
       </c>
       <c r="C140" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D140" s="0"/>
       <c r="E140" s="0"/>
@@ -4985,10 +4985,10 @@
         <v>1</v>
       </c>
       <c r="D141" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E141" s="0" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="F141" s="0" t="s">
         <v>109</v>
@@ -5007,7 +5007,7 @@
         <v>118</v>
       </c>
       <c r="L141" s="0" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="142">
@@ -5043,16 +5043,16 @@
         <v>71</v>
       </c>
       <c r="B143" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C143" s="0">
         <v>1</v>
       </c>
       <c r="D143" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E143" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F143" s="0" t="s">
         <v>109</v>
@@ -5068,10 +5068,10 @@
         <v>115</v>
       </c>
       <c r="K143" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L143" s="0" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="144">
@@ -5107,16 +5107,16 @@
         <v>72</v>
       </c>
       <c r="B145" s="0" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C145" s="0">
         <v>1</v>
       </c>
       <c r="D145" s="0" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E145" s="0" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="F145" s="0" t="s">
         <v>109</v>
@@ -5129,13 +5129,13 @@
         <v>113</v>
       </c>
       <c r="J145" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K145" s="0" t="s">
         <v>119</v>
       </c>
       <c r="L145" s="0" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="146">
@@ -5146,7 +5146,7 @@
         <v>2</v>
       </c>
       <c r="C146" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D146" s="0"/>
       <c r="E146" s="0"/>
@@ -5171,16 +5171,16 @@
         <v>73</v>
       </c>
       <c r="B147" s="0" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C147" s="0">
         <v>1</v>
       </c>
       <c r="D147" s="0" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E147" s="0" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="F147" s="0" t="s">
         <v>109</v>
@@ -5193,13 +5193,13 @@
         <v>113</v>
       </c>
       <c r="J147" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K147" s="0" t="s">
         <v>120</v>
       </c>
       <c r="L147" s="0" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="148">
@@ -5210,7 +5210,7 @@
         <v>2</v>
       </c>
       <c r="C148" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D148" s="0"/>
       <c r="E148" s="0"/>
@@ -5235,16 +5235,16 @@
         <v>74</v>
       </c>
       <c r="B149" s="0" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C149" s="0">
         <v>1</v>
       </c>
       <c r="D149" s="0" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E149" s="0" t="s">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="F149" s="0" t="s">
         <v>109</v>
@@ -5257,13 +5257,13 @@
         <v>113</v>
       </c>
       <c r="J149" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K149" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L149" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="150">
@@ -5274,7 +5274,7 @@
         <v>2</v>
       </c>
       <c r="C150" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D150" s="0"/>
       <c r="E150" s="0"/>
@@ -5299,16 +5299,16 @@
         <v>75</v>
       </c>
       <c r="B151" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C151" s="0">
         <v>1</v>
       </c>
       <c r="D151" s="0" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E151" s="0" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="F151" s="0" t="s">
         <v>109</v>
@@ -5324,10 +5324,10 @@
         <v>116</v>
       </c>
       <c r="K151" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L151" s="0" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="152">
@@ -5338,7 +5338,7 @@
         <v>2</v>
       </c>
       <c r="C152" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D152" s="0"/>
       <c r="E152" s="0"/>
@@ -5363,16 +5363,16 @@
         <v>76</v>
       </c>
       <c r="B153" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C153" s="0">
         <v>1</v>
       </c>
       <c r="D153" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E153" s="0" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="F153" s="0" t="s">
         <v>109</v>
@@ -5388,10 +5388,10 @@
         <v>116</v>
       </c>
       <c r="K153" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L153" s="0" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="154">
@@ -5402,7 +5402,7 @@
         <v>2</v>
       </c>
       <c r="C154" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D154" s="0"/>
       <c r="E154" s="0"/>
@@ -5433,10 +5433,10 @@
         <v>1</v>
       </c>
       <c r="D155" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E155" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F155" s="0" t="s">
         <v>109</v>
@@ -5497,10 +5497,10 @@
         <v>1</v>
       </c>
       <c r="D157" s="0" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E157" s="0" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="F157" s="0" t="s">
         <v>109</v>
@@ -5519,7 +5519,7 @@
         <v>120</v>
       </c>
       <c r="L157" s="0" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="158">
@@ -5561,10 +5561,10 @@
         <v>1</v>
       </c>
       <c r="D159" s="0" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E159" s="0" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="F159" s="0" t="s">
         <v>109</v>
@@ -5583,7 +5583,7 @@
         <v>119</v>
       </c>
       <c r="L159" s="0" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="160">
@@ -5594,7 +5594,7 @@
         <v>2</v>
       </c>
       <c r="C160" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D160" s="0"/>
       <c r="E160" s="0"/>
@@ -5625,10 +5625,10 @@
         <v>1</v>
       </c>
       <c r="D161" s="0" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E161" s="0" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F161" s="0" t="s">
         <v>109</v>
@@ -5647,7 +5647,7 @@
         <v>118</v>
       </c>
       <c r="L161" s="0" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
     </row>
     <row r="162">
@@ -5689,10 +5689,10 @@
         <v>1</v>
       </c>
       <c r="D163" s="0" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E163" s="0" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F163" s="0" t="s">
         <v>109</v>
@@ -5711,7 +5711,7 @@
         <v>118</v>
       </c>
       <c r="L163" s="0" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="164">
@@ -5747,16 +5747,16 @@
         <v>82</v>
       </c>
       <c r="B165" s="0" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C165" s="0">
         <v>1</v>
       </c>
       <c r="D165" s="0" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E165" s="0" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="F165" s="0" t="s">
         <v>109</v>
@@ -5772,10 +5772,10 @@
         <v>116</v>
       </c>
       <c r="K165" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L165" s="0" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="166">
@@ -5786,7 +5786,7 @@
         <v>2</v>
       </c>
       <c r="C166" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D166" s="0"/>
       <c r="E166" s="0"/>
@@ -5811,16 +5811,16 @@
         <v>83</v>
       </c>
       <c r="B167" s="0" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C167" s="0">
         <v>1</v>
       </c>
       <c r="D167" s="0" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E167" s="0" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F167" s="0" t="s">
         <v>109</v>
@@ -5836,10 +5836,10 @@
         <v>115</v>
       </c>
       <c r="K167" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L167" s="0" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
     </row>
     <row r="168">
@@ -5875,16 +5875,16 @@
         <v>84</v>
       </c>
       <c r="B169" s="0" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C169" s="0">
         <v>1</v>
       </c>
       <c r="D169" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E169" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F169" s="0" t="s">
         <v>109</v>
@@ -5900,10 +5900,10 @@
         <v>115</v>
       </c>
       <c r="K169" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L169" s="0" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="170">
@@ -5945,10 +5945,10 @@
         <v>1</v>
       </c>
       <c r="D171" s="0" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E171" s="0" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="F171" s="0" t="s">
         <v>109</v>
@@ -5967,7 +5967,7 @@
         <v>118</v>
       </c>
       <c r="L171" s="0" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="172">
@@ -6003,16 +6003,16 @@
         <v>86</v>
       </c>
       <c r="B173" s="0" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C173" s="0">
         <v>1</v>
       </c>
       <c r="D173" s="0" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E173" s="0" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F173" s="0" t="s">
         <v>109</v>
@@ -6028,10 +6028,10 @@
         <v>115</v>
       </c>
       <c r="K173" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L173" s="0" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="174">
@@ -6042,7 +6042,7 @@
         <v>2</v>
       </c>
       <c r="C174" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D174" s="0"/>
       <c r="E174" s="0"/>
@@ -6073,10 +6073,10 @@
         <v>1</v>
       </c>
       <c r="D175" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E175" s="0" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="F175" s="0" t="s">
         <v>109</v>
@@ -6095,7 +6095,7 @@
         <v>118</v>
       </c>
       <c r="L175" s="0" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
     </row>
     <row r="176">
@@ -6106,7 +6106,7 @@
         <v>2</v>
       </c>
       <c r="C176" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D176" s="0"/>
       <c r="E176" s="0"/>
@@ -6137,10 +6137,10 @@
         <v>1</v>
       </c>
       <c r="D177" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E177" s="0" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F177" s="0" t="s">
         <v>109</v>
@@ -6159,7 +6159,7 @@
         <v>119</v>
       </c>
       <c r="L177" s="0" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="178">
@@ -6170,7 +6170,7 @@
         <v>2</v>
       </c>
       <c r="C178" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D178" s="0"/>
       <c r="E178" s="0"/>
@@ -6195,16 +6195,16 @@
         <v>89</v>
       </c>
       <c r="B179" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C179" s="0">
         <v>1</v>
       </c>
       <c r="D179" s="0" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E179" s="0" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F179" s="0" t="s">
         <v>109</v>
@@ -6220,10 +6220,10 @@
         <v>115</v>
       </c>
       <c r="K179" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L179" s="0" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
     </row>
     <row r="180">
@@ -6259,16 +6259,16 @@
         <v>90</v>
       </c>
       <c r="B181" s="0" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C181" s="0">
         <v>1</v>
       </c>
       <c r="D181" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E181" s="0" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="F181" s="0" t="s">
         <v>109</v>
@@ -6281,13 +6281,13 @@
         <v>113</v>
       </c>
       <c r="J181" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K181" s="0" t="s">
         <v>119</v>
       </c>
       <c r="L181" s="0" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="182">
@@ -6298,7 +6298,7 @@
         <v>2</v>
       </c>
       <c r="C182" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D182" s="0"/>
       <c r="E182" s="0"/>
@@ -6323,16 +6323,16 @@
         <v>91</v>
       </c>
       <c r="B183" s="0" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C183" s="0">
         <v>1</v>
       </c>
       <c r="D183" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E183" s="0" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="F183" s="0" t="s">
         <v>109</v>
@@ -6345,13 +6345,13 @@
         <v>113</v>
       </c>
       <c r="J183" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K183" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L183" s="0" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
     </row>
     <row r="184">
@@ -6362,7 +6362,7 @@
         <v>2</v>
       </c>
       <c r="C184" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D184" s="0"/>
       <c r="E184" s="0"/>
@@ -6387,16 +6387,16 @@
         <v>92</v>
       </c>
       <c r="B185" s="0" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C185" s="0">
         <v>1</v>
       </c>
       <c r="D185" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E185" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F185" s="0" t="s">
         <v>109</v>
@@ -6412,10 +6412,10 @@
         <v>115</v>
       </c>
       <c r="K185" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L185" s="0" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="186">
@@ -6426,7 +6426,7 @@
         <v>2</v>
       </c>
       <c r="C186" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D186" s="0"/>
       <c r="E186" s="0"/>
@@ -6451,16 +6451,16 @@
         <v>93</v>
       </c>
       <c r="B187" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C187" s="0">
         <v>1</v>
       </c>
       <c r="D187" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E187" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F187" s="0" t="s">
         <v>109</v>
@@ -6476,10 +6476,10 @@
         <v>115</v>
       </c>
       <c r="K187" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L187" s="0" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="188">
@@ -6490,7 +6490,7 @@
         <v>2</v>
       </c>
       <c r="C188" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D188" s="0"/>
       <c r="E188" s="0"/>
@@ -6515,7 +6515,7 @@
         <v>94</v>
       </c>
       <c r="B189" s="0" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C189" s="0">
         <v>1</v>
@@ -6524,26 +6524,26 @@
         <v>102</v>
       </c>
       <c r="E189" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F189" s="0" t="s">
         <v>109</v>
       </c>
       <c r="G189" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H189" s="0"/>
       <c r="I189" s="0" t="s">
         <v>113</v>
       </c>
       <c r="J189" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K189" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L189" s="0" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="190">
@@ -6554,7 +6554,7 @@
         <v>2</v>
       </c>
       <c r="C190" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D190" s="0"/>
       <c r="E190" s="0"/>
@@ -6579,7 +6579,7 @@
         <v>95</v>
       </c>
       <c r="B191" s="0" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C191" s="0">
         <v>1</v>
@@ -6588,7 +6588,7 @@
         <v>103</v>
       </c>
       <c r="E191" s="0" t="s">
-        <v>103</v>
+        <v>37</v>
       </c>
       <c r="F191" s="0" t="s">
         <v>109</v>
@@ -6601,13 +6601,13 @@
         <v>113</v>
       </c>
       <c r="J191" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K191" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L191" s="0" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="192">
@@ -6618,7 +6618,7 @@
         <v>2</v>
       </c>
       <c r="C192" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D192" s="0"/>
       <c r="E192" s="0"/>
@@ -6643,7 +6643,7 @@
         <v>96</v>
       </c>
       <c r="B193" s="0" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C193" s="0">
         <v>1</v>
@@ -6668,10 +6668,10 @@
         <v>115</v>
       </c>
       <c r="K193" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L193" s="0" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="194">
@@ -6707,7 +6707,7 @@
         <v>97</v>
       </c>
       <c r="B195" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C195" s="0">
         <v>1</v>
@@ -6716,7 +6716,7 @@
         <v>105</v>
       </c>
       <c r="E195" s="0" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="F195" s="0" t="s">
         <v>109</v>
@@ -6732,10 +6732,10 @@
         <v>116</v>
       </c>
       <c r="K195" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L195" s="0" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="196">
@@ -6771,7 +6771,7 @@
         <v>98</v>
       </c>
       <c r="B197" s="0" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C197" s="0">
         <v>1</v>
@@ -6780,7 +6780,7 @@
         <v>106</v>
       </c>
       <c r="E197" s="0" t="s">
-        <v>37</v>
+        <v>106</v>
       </c>
       <c r="F197" s="0" t="s">
         <v>109</v>
@@ -6793,13 +6793,13 @@
         <v>113</v>
       </c>
       <c r="J197" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K197" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L197" s="0" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="198">
